--- a/tests/MES.SPC.E2ETests/bin/Debug/net10.0/Fixtures/variable_upload_valid.xlsx
+++ b/tests/MES.SPC.E2ETests/bin/Debug/net10.0/Fixtures/variable_upload_valid.xlsx
@@ -55,40 +55,40 @@
     <x:t>LEN-001</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-05-21 03:16:59</x:t>
+    <x:t>2026-05-31 08:48:10</x:t>
   </x:si>
   <x:si>
     <x:t>E2E-OP</x:t>
   </x:si>
   <x:si>
-    <x:t>L-E2E-OK-20260521032659</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-21 03:17:59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-21 03:18:59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-21 03:19:59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-21 03:20:59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-21 03:21:59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-21 03:22:59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-21 03:23:59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-21 03:24:59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-21 03:25:59</x:t>
+    <x:t>L-E2E-OK-20260531085810</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-31 08:49:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-31 08:50:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-31 08:51:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-31 08:52:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-31 08:53:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-31 08:54:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-31 08:55:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-31 08:56:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-31 08:57:10</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/tests/MES.SPC.E2ETests/bin/Debug/net10.0/Fixtures/variable_upload_valid.xlsx
+++ b/tests/MES.SPC.E2ETests/bin/Debug/net10.0/Fixtures/variable_upload_valid.xlsx
@@ -55,40 +55,40 @@
     <x:t>LEN-001</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-05-31 08:48:10</x:t>
+    <x:t>2026-06-08 09:01:38</x:t>
   </x:si>
   <x:si>
     <x:t>E2E-OP</x:t>
   </x:si>
   <x:si>
-    <x:t>L-E2E-OK-20260531085810</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-31 08:49:10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-31 08:50:10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-31 08:51:10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-31 08:52:10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-31 08:53:10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-31 08:54:10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-31 08:55:10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-31 08:56:10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-31 08:57:10</x:t>
+    <x:t>L-E2E-OK-20260608091138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-08 09:02:38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-08 09:03:38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-08 09:04:38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-08 09:05:38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-08 09:06:38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-08 09:07:38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-08 09:08:38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-08 09:09:38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-08 09:10:38</x:t>
   </x:si>
 </x:sst>
 </file>
